--- a/data/xlsx/pksf--refrigeration-and-air-conditioning.xlsx
+++ b/data/xlsx/pksf--refrigeration-and-air-conditioning.xlsx
@@ -646,7 +646,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>10</v>
       </c>
@@ -668,7 +670,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>9</v>
       </c>
@@ -690,7 +694,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -712,7 +718,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -734,7 +742,9 @@
       <c r="C20" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>7</v>
       </c>
@@ -756,7 +766,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>8</v>
       </c>
@@ -778,7 +790,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>7</v>
       </c>
@@ -800,7 +814,9 @@
       <c r="C23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -822,7 +838,9 @@
       <c r="C24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>5</v>
       </c>
@@ -844,7 +862,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>6</v>
       </c>
@@ -866,7 +886,9 @@
       <c r="C26" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -888,7 +910,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -910,7 +934,9 @@
       <c r="C28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>4</v>
       </c>
@@ -932,7 +958,9 @@
       <c r="C29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>5</v>
       </c>
@@ -954,7 +982,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>4</v>
       </c>
@@ -976,7 +1006,9 @@
       <c r="C31" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -998,7 +1030,9 @@
       <c r="C32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>7</v>
       </c>
@@ -1020,7 +1054,9 @@
       <c r="C33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>5</v>
       </c>

--- a/data/xlsx/pksf--refrigeration-and-air-conditioning.xlsx
+++ b/data/xlsx/pksf--refrigeration-and-air-conditioning.xlsx
@@ -99,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -132,6 +132,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -635,7 +641,7 @@
       </c>
     </row>
     <row r="16" ht="14.15" customHeight="1">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="14" t="n">
         <v>1</v>
       </c>
       <c r="B16" s="8" t="inlineStr">
@@ -650,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(MIN(C16,D16)*E16/C16,0)</f>
@@ -659,7 +665,7 @@
       <c r="G16" s="9" t="n"/>
     </row>
     <row r="17" ht="14.15" customHeight="1">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="14" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -674,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" s="9">
         <f>IFERROR(MIN(C17,D17)*E17/C17,0)</f>
@@ -683,7 +689,7 @@
       <c r="G17" s="9" t="n"/>
     </row>
     <row r="18" ht="14.15" customHeight="1">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="8" t="inlineStr">
@@ -698,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" s="9">
         <f>IFERROR(MIN(C18,D18)*E18/C18,0)</f>
@@ -707,7 +713,7 @@
       <c r="G18" s="9" t="n"/>
     </row>
     <row r="19" ht="14.15" customHeight="1">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="14" t="n">
         <v>4</v>
       </c>
       <c r="B19" s="8" t="inlineStr">
@@ -731,7 +737,7 @@
       <c r="G19" s="9" t="n"/>
     </row>
     <row r="20" ht="14.15" customHeight="1">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B20" s="8" t="inlineStr">
@@ -746,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="9">
         <f>IFERROR(MIN(C20,D20)*E20/C20,0)</f>
@@ -755,7 +761,7 @@
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21" ht="14.15" customHeight="1">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="14" t="n">
         <v>6</v>
       </c>
       <c r="B21" s="8" t="inlineStr">
@@ -770,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F21" s="9">
         <f>IFERROR(MIN(C21,D21)*E21/C21,0)</f>
@@ -779,7 +785,7 @@
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22" ht="14.15" customHeight="1">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="14" t="n">
         <v>7</v>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -794,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(MIN(C22,D22)*E22/C22,0)</f>
@@ -803,7 +809,7 @@
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23" ht="14.15" customHeight="1">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="14" t="n">
         <v>8</v>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -818,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="9">
         <f>IFERROR(MIN(C23,D23)*E23/C23,0)</f>
@@ -827,7 +833,7 @@
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24" ht="14.15" customHeight="1">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="14" t="n">
         <v>9</v>
       </c>
       <c r="B24" s="8" t="inlineStr">
@@ -842,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(MIN(C24,D24)*E24/C24,0)</f>
@@ -851,7 +857,7 @@
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25" ht="14.15" customHeight="1">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="14" t="n">
         <v>10</v>
       </c>
       <c r="B25" s="8" t="inlineStr">
@@ -866,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F25" s="9">
         <f>IFERROR(MIN(C25,D25)*E25/C25,0)</f>
@@ -875,7 +881,7 @@
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26" ht="14.15" customHeight="1">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="14" t="n">
         <v>11</v>
       </c>
       <c r="B26" s="8" t="inlineStr">
@@ -890,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(MIN(C26,D26)*E26/C26,0)</f>
@@ -899,7 +905,7 @@
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27" ht="14.15" customHeight="1">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="14" t="n">
         <v>12</v>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -914,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F27" s="9">
         <f>IFERROR(MIN(C27,D27)*E27/C27,0)</f>
@@ -923,7 +929,7 @@
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28" ht="14.15" customHeight="1">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="14" t="n">
         <v>13</v>
       </c>
       <c r="B28" s="8" t="inlineStr">
@@ -947,7 +953,7 @@
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29" ht="14.15" customHeight="1">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="B29" s="8" t="inlineStr">
@@ -971,7 +977,7 @@
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30" ht="14.15" customHeight="1">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="14" t="n">
         <v>15</v>
       </c>
       <c r="B30" s="8" t="inlineStr">
@@ -995,7 +1001,7 @@
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31" ht="14.15" customHeight="1">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="14" t="n">
         <v>16</v>
       </c>
       <c r="B31" s="8" t="inlineStr">
@@ -1019,7 +1025,7 @@
       <c r="G31" s="9" t="n"/>
     </row>
     <row r="32" ht="14.15" customHeight="1">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="14" t="n">
         <v>17</v>
       </c>
       <c r="B32" s="8" t="inlineStr">
@@ -1034,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(MIN(C32,D32)*E32/C32,0)</f>
@@ -1043,7 +1049,7 @@
       <c r="G32" s="9" t="n"/>
     </row>
     <row r="33" ht="14.15" customHeight="1">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="14" t="n">
         <v>18</v>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -1067,7 +1073,7 @@
       <c r="G33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Sum</t>
         </is>
@@ -1075,18 +1081,18 @@
       <c r="B34" s="11" t="n"/>
       <c r="C34" s="11" t="n"/>
       <c r="D34" s="12" t="n"/>
-      <c r="E34" s="10">
+      <c r="E34" s="15">
         <f>SUM(E16:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="15">
         <f>SUM(F16:F33)</f>
         <v/>
       </c>
       <c r="G34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Score out of 100</t>
         </is>
@@ -1095,7 +1101,7 @@
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="12" t="n"/>
-      <c r="F35" s="10">
+      <c r="F35" s="15">
         <f>F34/E34*100</f>
         <v/>
       </c>
@@ -1103,7 +1109,7 @@
     </row>
     <row r="36" ht="9.75" customHeight="1"/>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Total achieved points out of 30  </t>
         </is>
@@ -1112,11 +1118,11 @@
       <c r="C37" s="11" t="n"/>
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="12" t="n"/>
-      <c r="F37" s="10">
+      <c r="F37" s="15">
         <f>F35*30/100</f>
         <v/>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
